--- a/stories/arbres/ATOM-LAN.MOT.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Papa pose deux paniers sur la table. Dans un saladier, il y a une pomme, une banane, un chapeau, une chaussette. Géraldine regarde. Papa dit : on range par catégorie. Les fruits ensemble. Les habits ensemble. Géraldine prend la pomme. Elle la met avec la banane. C'est la catégorie des fruits. Elle prend le chapeau. Elle le met avec la chaussette. C'est la catégorie des habits. Papa dit : tu as classé. Géraldine nomme : pomme, banane. Fruits. Chapeau, chaussette. Habits. Deux catégories. Papa sourit. Géraldine range encore une poire avec les fruits.</t>
+          <t>Papa pose deux paniers sur la table. Dans un saladier, il y a une pomme, une banane, un chapeau, une chaussette. Géraldine regarde. On range par catégorie. Les fruits ensemble. Les habits ensemble. Géraldine prend la pomme. Elle la met avec la banane. C'est la catégorie des fruits. Elle prend le chapeau. Elle le met avec la chaussette. C'est la catégorie des habits. Tu as classé. Géraldine nomme : pomme, banane. Fruits. Chapeau, chaussette. Habits. Deux catégories. Papa sourit. Géraldine range encore une poire avec les fruits.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Papa pose deux paniers sur la table. Dans un saladier, il y a une pomme, une banane, un chapeau, une chaussette. Géraldine regarde.
+papa|On range par catégorie.
+narrateur|Les fruits ensemble. Les habits ensemble. Géraldine prend la pomme. Elle la met avec la banane. C'est la catégorie des fruits. Elle prend le chapeau. Elle le met avec la chaussette. C'est la catégorie des habits.
+papa|Tu as classé.
+narrateur|Géraldine nomme : pomme, banane. Fruits. Chapeau, chaussette. Habits. Deux catégories. Papa sourit. Géraldine range encore une poire avec les fruits.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Géraldine range pomme et chapeau. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Géraldine a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Géraldine pose la poire. Les deux paniers sont rangés.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Géraldine nomme : pomme, banane. Fruits. Chapeau, chaussette. Habits. Deux catégories. Papa sourit. Géraldine range encore une poire avec les fruits.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Géraldine range pomme et chapeau. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Géraldine a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Géraldine pose la poire. Les deux paniers sont rangés.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.MOT.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Géraldine classe fruits et habits</t>
+          <t>Les deux paniers de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deux paniers vides attendent sur la table tiède. Sarah nomme pomme et banane, chapeau et chaussette, puis range encore une poire.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Papa pose deux paniers sur la table. Dans un saladier, il y a une pomme, une banane, un chapeau, une chaussette. Géraldine regarde. On range par catégorie. Les fruits ensemble. Les habits ensemble. Géraldine prend la pomme. Elle la met avec la banane. C'est la catégorie des fruits. Elle prend le chapeau. Elle le met avec la chaussette. C'est la catégorie des habits. Tu as classé. Géraldine nomme : pomme, banane. Fruits. Chapeau, chaussette. Habits. Deux catégories. Papa sourit. Géraldine range encore une poire avec les fruits.</t>
+          <t>Deux paniers vides attendent, côte à côte. Un chapeau sent encore la pluie. Le bois de la table est tiède. Le soleil de fin d'après-midi pose une barre d'or. Une banane courbe fait une ombre sur le saladier. Une chaise racle, puis se tait. Sarah, tu vois les deux paniers ? Ils sont vides, pour l'instant. Oui, papa. Ils se touchent presque. Le saladier s'est mélangé. On range par catégorie. En ce moment, Sarah s'approche de la table. Dans le saladier, il y a une pomme. Une banane. Un chapeau. Une chaussette. Le chapeau est encore un peu mouillé. Les fruits ensemble. Les habits ensemble. Sarah prend la pomme. Elle est lisse, un peu froide. Pomme. C'est un fruit. Mets-la dans ce panier. Sarah pose la pomme dans le premier panier. Elle prend la banane. La peau est un peu collante au bout. Banane. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Sarah met la banane avec la pomme. Elle prend le chapeau. Le bord est encore frais de pluie. Chapeau. C'est un habit. Oui. L'autre panier, maintenant. Sarah pose le chapeau dans le second panier. Elle prend la chaussette. La chaussette est douce, un peu roulée. Chaussette. C'est un habit. Les habits ensemble. C'est une catégorie. Sarah met la chaussette avec le chapeau. Catégorie. Pomme, banane. Fruits. Chapeau, chaussette. Habits. Tu as classé. Bravo, Sarah. Tu as nommé. Tu as mis ensemble. C'est du bon travail. Papa sort encore une poire du saladier. Et celle-là ? Poire. C'est un fruit. Sarah range la poire avec les fruits. Tu as fini les deux paniers ? Oui, papa. Les deux paniers ne sont plus vides. La barre d'or a glissé un peu sur le bois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,72 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Papa pose deux paniers sur la table. Dans un saladier, il y a une pomme, une banane, un chapeau, une chaussette. Géraldine regarde.
+          <t>narrateur|Deux paniers vides attendent, côte à côte.
+narrateur|Un chapeau sent encore la pluie.
+narrateur|Le bois de la table est tiède.
+narrateur|Le soleil de fin d'après-midi pose une barre d'or.
+narrateur|Une banane courbe fait une ombre sur le saladier.
+narrateur|Une chaise racle, puis se tait.
+papa|Sarah, tu vois les deux paniers ?
+papa|Ils sont vides, pour l'instant.
+enfant-f|Oui, papa.
+enfant-f|Ils se touchent presque.
+papa|Le saladier s'est mélangé.
 papa|On range par catégorie.
-narrateur|Les fruits ensemble. Les habits ensemble. Géraldine prend la pomme. Elle la met avec la banane. C'est la catégorie des fruits. Elle prend le chapeau. Elle le met avec la chaussette. C'est la catégorie des habits.
+narrateur|En ce moment, Sarah s'approche de la table.
+narrateur|Dans le saladier, il y a une pomme.
+narrateur|Une banane.
+narrateur|Un chapeau.
+narrateur|Une chaussette.
+enfant-f|Le chapeau est encore un peu mouillé.
+papa|Les fruits ensemble.
+papa|Les habits ensemble.
+narrateur|Sarah prend la pomme.
+narrateur|Elle est lisse, un peu froide.
+enfant-f|Pomme.
+enfant-f|C'est un fruit.
+papa|Mets-la dans ce panier.
+narrateur|Sarah pose la pomme dans le premier panier.
+narrateur|Elle prend la banane.
+narrateur|La peau est un peu collante au bout.
+enfant-f|Banane.
+enfant-f|C'est un fruit aussi.
+papa|Les fruits ensemble.
+papa|C'est une catégorie.
+narrateur|Sarah met la banane avec la pomme.
+narrateur|Elle prend le chapeau.
+narrateur|Le bord est encore frais de pluie.
+enfant-f|Chapeau.
+enfant-f|C'est un habit.
+papa|Oui.
+papa|L'autre panier, maintenant.
+narrateur|Sarah pose le chapeau dans le second panier.
+narrateur|Elle prend la chaussette.
+narrateur|La chaussette est douce, un peu roulée.
+enfant-f|Chaussette.
+enfant-f|C'est un habit.
+papa|Les habits ensemble.
+papa|C'est une catégorie.
+narrateur|Sarah met la chaussette avec le chapeau.
+enfant-f|Catégorie.
+enfant-f|Pomme, banane.
+enfant-f|Fruits.
+enfant-f|Chapeau, chaussette.
+enfant-f|Habits.
 papa|Tu as classé.
-narrateur|Géraldine nomme : pomme, banane. Fruits. Chapeau, chaussette. Habits. Deux catégories. Papa sourit. Géraldine range encore une poire avec les fruits.</t>
+papa|Bravo, Sarah.
+papa|Tu as nommé.
+papa|Tu as mis ensemble.
+papa|C'est du bon travail.
+narrateur|Papa sort encore une poire du saladier.
+papa|Et celle-là ?
+enfant-f|Poire.
+enfant-f|C'est un fruit.
+narrateur|Sarah range la poire avec les fruits.
+papa|Tu as fini les deux paniers ?
+enfant-f|Oui, papa.
+narrateur|Les deux paniers ne sont plus vides.
+narrateur|La barre d'or a glissé un peu sur le bois.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1417,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Géraldine range pomme et chapeau. Que fait-elle ?</t>
+          <t>Sarah range pomme et chapeau. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1573,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Géraldine range pomme et chapeau. Que fait-elle ?</t>
+          <t>narrateur|Sarah range pomme et chapeau.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Géraldine a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Papa était là.</t>
+          <t>Sarah a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo. C'est du bon travail, Sarah. Le premier panier ? Les fruits. Le second ? Les habits. Deux paniers, deux catégories. Oui, papa. La table est claire, maintenant. Les paniers se touchent encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1746,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Géraldine a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Papa était là.</t>
+          <t>narrateur|Sarah a classé.
+narrateur|Une catégorie pour les fruits.
+narrateur|Une catégorie pour les habits.
+papa|Tu as mis ensemble.
+papa|Bravo.
+papa|C'est du bon travail, Sarah.
+papa|Le premier panier ?
+enfant-f|Les fruits.
+papa|Le second ?
+enfant-f|Les habits.
+papa|Deux paniers, deux catégories.
+enfant-f|Oui, papa.
+narrateur|La table est claire, maintenant.
+narrateur|Les paniers se touchent encore.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1787,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Géraldine pose la poire. Les deux paniers sont rangés.</t>
+          <t>Sarah pose encore la poire, bien au milieu. Les deux paniers sont rangés. On croque la pomme ? Oui, papa. La pomme craque. Le jus est froid. Le chapeau sèche sur le dossier, maintenant. Il sent moins la pluie. Les fruits restent dans leur panier. Les habits dans l'autre. Le soleil quitte presque la table. Tu as classé, puis tu croques. Les paniers sont pleins.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,7 +1923,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Géraldine pose la poire. Les deux paniers sont rangés.</t>
+          <t>narrateur|Sarah pose encore la poire, bien au milieu.
+narrateur|Les deux paniers sont rangés.
+papa|On croque la pomme ?
+enfant-f|Oui, papa.
+narrateur|La pomme craque.
+narrateur|Le jus est froid.
+papa|Le chapeau sèche sur le dossier, maintenant.
+enfant-f|Il sent moins la pluie.
+papa|Les fruits restent dans leur panier.
+enfant-f|Les habits dans l'autre.
+narrateur|Le soleil quitte presque la table.
+papa|Tu as classé, puis tu croques.
+enfant-f|Les paniers sont pleins.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1864,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai classé. Deux catégories. Bravo. Tu as fait du bon travail. Les deux paniers se touchent encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,7 +2103,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai classé.
+enfant-f|Deux catégories.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Les deux paniers se touchent encore.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2026,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Deux paniers vides attendent, côte à côte. Un chapeau sent encore la pluie. Le bois de la table est tiède. Le soleil de fin d'après-midi pose une barre d'or. Une banane courbe fait une ombre sur le saladier. Une chaise racle, puis se tait. Sarah, tu vois les deux paniers ? Ils sont vides, pour l'instant. Oui, papa. Ils se touchent presque. Le saladier s'est mélangé. On range par catégorie. En ce moment, Sarah s'approche de la table. Dans le saladier, il y a une pomme. Une banane. Un chapeau. Une chaussette. Le chapeau est encore un peu mouillé. Les fruits ensemble. Les habits ensemble. Sarah prend la pomme. Elle est lisse, un peu froide. Pomme. C'est un fruit. Mets-la dans ce panier. Sarah pose la pomme dans le premier panier. Elle prend la banane. La peau est un peu collante au bout. Banane. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Sarah met la banane avec la pomme. Elle prend le chapeau. Le bord est encore frais de pluie. Chapeau. C'est un habit. Oui. L'autre panier, maintenant. Sarah pose le chapeau dans le second panier. Elle prend la chaussette. La chaussette est douce, un peu roulée. Chaussette. C'est un habit. Les habits ensemble. C'est une catégorie. Sarah met la chaussette avec le chapeau. Catégorie. Pomme, banane. Fruits. Chapeau, chaussette. Habits. Tu as classé. Bravo, Sarah. Tu as nommé. Tu as mis ensemble. C'est du bon travail. Papa sort encore une poire du saladier. Et celle-là ? Poire. C'est un fruit. Sarah range la poire avec les fruits. Tu as fini les deux paniers ? Oui, papa. Les deux paniers ne sont plus vides. La barre d'or a glissé un peu sur le bois.</t>
+          <t>Deux paniers vides attendent, côte à côte. Un chapeau sent encore la pluie. Le bois de la table est tiède. Le soleil de fin d'après-midi pose une barre d'or. Une banane courbe fait une ombre sur le saladier. Une chaise racle, puis se tait. Sarah, tu vois les deux paniers ? Ils sont vides, pour l'instant. Oui, papa. Ils se touchent presque. Le saladier s'est mélangé. On range par catégorie. En ce moment, Sarah s'approche de la table. Dans le saladier, il y a une pomme. Une banane. Un chapeau. Une chaussette. Le chapeau est encore un peu mouillé. Les fruits ensemble. Les habits ensemble. Sarah prend la pomme. Elle est lisse, un peu froide. Pomme. C'est un fruit. Mets-la dans ce panier. Sarah pose la pomme dans le premier panier. Elle prend la banane. La peau est un peu collante au bout. Banane. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Sarah met la banane avec la pomme. Elle prend le chapeau. Le bord est encore frais de pluie. Chapeau. C'est un habit. Oui. L'autre panier, maintenant. Sarah pose le chapeau dans le second panier. Elle prend la chaussette. La chaussette est douce, un peu roulée. Chaussette. C'est un habit. Les habits ensemble. C'est une catégorie. Sarah met la chaussette avec le chapeau. Catégorie. Pomme, banane. Fruits. Chapeau, chaussette. Habits. Tu as classé. Bravo, Sarah. Tu as nommé. Tu as mis ensemble. Papa sort encore une poire du saladier. Et celle-là ? Poire. C'est un fruit. Sarah range la poire avec les fruits. Tu as fini les deux paniers ? Oui, papa. Les deux paniers ne sont plus vides. La barre d'or a glissé un peu sur le bois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa pose deux paniers sur la table. Dans un saladier, il y a une pomme, une banane, un chapeau, une chaussette. Géraldine regarde. Papa dit : on range par &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt;. Les fruits ensemble. Les habits ensemble. Géraldine prend la pomme. Elle la met avec la banane. C'est la catégorie des fruits. Elle prend le chapeau. Elle le met avec la chaussette. C'est la catégorie des habits. Papa dit : tu as classé. Géraldine nomme : pomme, banane. Fruits. Chapeau, chaussette. Habits. Deux catégories. Papa sourit. Géraldine range encore une poire avec les fruits.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Deux paniers vides attendent, côte à côte. Un chapeau sent encore la pluie. Le bois de la table est tiède. Le soleil de fin d'après-midi pose une barre d'or. Une banane courbe fait une ombre sur le saladier. Une chaise racle, puis se tait. Sarah, tu vois les deux paniers ? Ils sont vides, pour l'instant. Oui, papa. Ils se touchent presque. Le saladier s'est mélangé. On range par catégorie. En ce moment, Sarah s'approche de la table. Dans le saladier, il y a une pomme. Une banane. Un chapeau. Une chaussette. Le chapeau est encore un peu mouillé. Les fruits ensemble. Les habits ensemble. Sarah prend la pomme. Elle est lisse, un peu froide. Pomme. C'est un fruit. Mets-la dans ce panier. Sarah pose la pomme dans le premier panier. Elle prend la banane. La peau est un peu collante au bout. Banane. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Sarah met la banane avec la pomme. Elle prend le chapeau. Le bord est encore frais de pluie. Chapeau. C'est un habit. Oui. L'autre panier, maintenant. Sarah pose le chapeau dans le second panier. Elle prend la chaussette. La chaussette est douce, un peu roulée. Chaussette. C'est un habit. Les habits ensemble. C'est une catégorie. Sarah met la chaussette avec le chapeau. Catégorie. Pomme, banane. Fruits. Chapeau, chaussette. Habits. Tu as classé. Bravo, Sarah. Tu as nommé. Tu as mis ensemble. Papa sort encore une poire du saladier. Et celle-là ? Poire. C'est un fruit. Sarah range la poire avec les fruits. Tu as fini les deux paniers ? Oui, papa. Les deux paniers ne sont plus vides. La barre d'or a glissé un peu sur le bois.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1380,7 +1380,6 @@
 papa|Bravo, Sarah.
 papa|Tu as nommé.
 papa|Tu as mis ensemble.
-papa|C'est du bon travail.
 narrateur|Papa sort encore une poire du saladier.
 papa|Et celle-là ?
 enfant-f|Poire.
@@ -1392,7 +1391,6 @@
 narrateur|La barre d'or a glissé un peu sur le bois.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1422,7 +1420,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Géraldine range pomme et chapeau. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah range pomme et chapeau. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1577,7 +1575,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1602,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo. C'est du bon travail, Sarah. Le premier panier ? Les fruits. Le second ? Les habits. Deux paniers, deux catégories. Oui, papa. La table est claire, maintenant. Les paniers se touchent encore.</t>
+          <t>Sarah a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo. Le premier panier ? Les fruits. Le second ? Les habits. Deux paniers, deux catégories. Oui, papa. La table est claire, maintenant. Les paniers se touchent encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Géraldine a classé. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une catégorie pour les habits. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo. Le premier panier ? Les fruits. Le second ? Les habits. Deux paniers, deux catégories. Oui, papa. La table est claire, maintenant. Les paniers se touchent encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1751,7 +1748,6 @@
 narrateur|Une catégorie pour les habits.
 papa|Tu as mis ensemble.
 papa|Bravo.
-papa|C'est du bon travail, Sarah.
 papa|Le premier panier ?
 enfant-f|Les fruits.
 papa|Le second ?
@@ -1762,7 +1758,6 @@
 narrateur|Les paniers se touchent encore.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1792,7 +1787,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Géraldine pose la poire. Les deux paniers sont rangés.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah pose encore la poire, bien au milieu. Les deux paniers sont rangés. On croque la pomme ? Oui, papa. La pomme craque. Le jus est froid. Le chapeau sèche sur le dossier, maintenant. Il sent moins la pluie. Les fruits restent dans leur panier. Les habits dans l'autre. Le soleil quitte presque la table. Tu as classé, puis tu croques. Les paniers sont pleins.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1938,7 +1933,6 @@
 enfant-f|Les paniers sont pleins.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1963,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai classé. Deux catégories. Bravo. Tu as fait du bon travail. Les deux paniers se touchent encore. L'histoire est finie.</t>
+          <t>J'ai classé. Deux catégories. Bravo. Les deux paniers se touchent encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai classé. Deux catégories. Bravo. Les deux paniers se touchent encore.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,12 +2100,9 @@
           <t>enfant-f|J'ai classé.
 enfant-f|Deux catégories.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Les deux paniers se touchent encore.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Les deux paniers se touchent encore.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2130,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2166,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Géraldine, papa</t>
+          <t>Sarah, papa</t>
         </is>
       </c>
     </row>
